--- a/artfynd/A 24124-2024 artfynd.xlsx
+++ b/artfynd/A 24124-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101709217</v>
+        <v>101709190</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>716819.3608097631</v>
+        <v>716898</v>
       </c>
       <c r="R2" t="n">
-        <v>7103875.799260718</v>
+        <v>7103919</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -791,42 +786,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101709200</v>
+        <v>101709204</v>
       </c>
       <c r="B3" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716560.9084873652</v>
+        <v>716467</v>
       </c>
       <c r="R3" t="n">
-        <v>7103801.8862592</v>
+        <v>7103640</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -907,37 +897,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101709235</v>
+        <v>101709240</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -951,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716670.3800777509</v>
+        <v>716484</v>
       </c>
       <c r="R4" t="n">
-        <v>7103787.056929761</v>
+        <v>7103593</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1026,12 +1011,7 @@
         <v>101709241</v>
       </c>
       <c r="B5" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716679.6190774869</v>
+        <v>716679</v>
       </c>
       <c r="R5" t="n">
-        <v>7103768.329789569</v>
+        <v>7103768</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1139,37 +1119,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>101709229</v>
+        <v>101709242</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1183,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>716523.3754338571</v>
+        <v>716540</v>
       </c>
       <c r="R6" t="n">
-        <v>7103638.143209356</v>
+        <v>7103765</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1255,37 +1230,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>101709202</v>
+        <v>101709217</v>
       </c>
       <c r="B7" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1299,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716601.9614205157</v>
+        <v>716819</v>
       </c>
       <c r="R7" t="n">
-        <v>7103807.385874188</v>
+        <v>7103876</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1371,19 +1341,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>101709233</v>
+        <v>101709219</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1415,10 +1380,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716568.0117237223</v>
+        <v>716817</v>
       </c>
       <c r="R8" t="n">
-        <v>7103813.826885701</v>
+        <v>7103882</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1487,37 +1452,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>101709214</v>
+        <v>101709220</v>
       </c>
       <c r="B9" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1531,10 +1491,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716524.3561109824</v>
+        <v>716580</v>
       </c>
       <c r="R9" t="n">
-        <v>7103643.054300413</v>
+        <v>7103753</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1603,19 +1563,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>101709230</v>
+        <v>101709222</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1647,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716539.1312864937</v>
+        <v>716403</v>
       </c>
       <c r="R10" t="n">
-        <v>7103652.447565395</v>
+        <v>7103688</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1719,19 +1674,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>101709219</v>
+        <v>101709223</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1763,10 +1713,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>716817.1786252772</v>
+        <v>716419</v>
       </c>
       <c r="R11" t="n">
-        <v>7103881.810397031</v>
+        <v>7103690</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1835,37 +1785,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>101709205</v>
+        <v>101709224</v>
       </c>
       <c r="B12" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1879,10 +1824,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>716767.3308628566</v>
+        <v>716451</v>
       </c>
       <c r="R12" t="n">
-        <v>7103863.36854683</v>
+        <v>7103672</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1951,19 +1896,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>101709222</v>
+        <v>101709225</v>
       </c>
       <c r="B13" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1995,10 +1935,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>716403.5345586376</v>
+        <v>716466</v>
       </c>
       <c r="R13" t="n">
-        <v>7103687.918082361</v>
+        <v>7103651</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2067,37 +2007,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>101709190</v>
+        <v>101709227</v>
       </c>
       <c r="B14" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2111,10 +2046,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716897.449113213</v>
+        <v>716470</v>
       </c>
       <c r="R14" t="n">
-        <v>7103919.102818635</v>
+        <v>7103649</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2183,37 +2118,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>101709195</v>
+        <v>101709229</v>
       </c>
       <c r="B15" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2227,10 +2157,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>716767.3308628566</v>
+        <v>716523</v>
       </c>
       <c r="R15" t="n">
-        <v>7103863.36854683</v>
+        <v>7103638</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2299,19 +2229,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>101709234</v>
+        <v>101709230</v>
       </c>
       <c r="B16" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2343,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>716670.5362940163</v>
+        <v>716539</v>
       </c>
       <c r="R16" t="n">
-        <v>7103753.169097384</v>
+        <v>7103652</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2415,37 +2340,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>101709242</v>
+        <v>101709232</v>
       </c>
       <c r="B17" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2459,10 +2379,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>716540.5368019766</v>
+        <v>716592</v>
       </c>
       <c r="R17" t="n">
-        <v>7103765.249067678</v>
+        <v>7103675</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2531,15 +2451,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>101709204</v>
+        <v>101709233</v>
       </c>
       <c r="B18" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2547,21 +2462,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2575,10 +2490,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>716467.2942132897</v>
+        <v>716568</v>
       </c>
       <c r="R18" t="n">
-        <v>7103639.523607221</v>
+        <v>7103814</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2647,19 +2562,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>101709227</v>
+        <v>101709234</v>
       </c>
       <c r="B19" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2691,10 +2601,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716470.194112177</v>
+        <v>716671</v>
       </c>
       <c r="R19" t="n">
-        <v>7103648.530510771</v>
+        <v>7103753</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2763,19 +2673,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>101709220</v>
+        <v>101709235</v>
       </c>
       <c r="B20" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2807,10 +2712,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>716579.7395170134</v>
+        <v>716670</v>
       </c>
       <c r="R20" t="n">
-        <v>7103753.009898473</v>
+        <v>7103787</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2879,15 +2784,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>101709238</v>
+        <v>101709202</v>
       </c>
       <c r="B21" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2895,26 +2795,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219790</v>
+        <v>6456</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2923,10 +2823,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>716560.9084873652</v>
+        <v>716602</v>
       </c>
       <c r="R21" t="n">
-        <v>7103801.8862592</v>
+        <v>7103807</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2998,12 +2898,7 @@
         <v>101709203</v>
       </c>
       <c r="B22" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,10 +2934,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>716620.4806535994</v>
+        <v>716620</v>
       </c>
       <c r="R22" t="n">
-        <v>7103775.65748985</v>
+        <v>7103775</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3111,37 +3006,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>101709239</v>
+        <v>101709205</v>
       </c>
       <c r="B23" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3155,10 +3045,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>716559.7988201906</v>
+        <v>716767</v>
       </c>
       <c r="R23" t="n">
-        <v>7103811.49419031</v>
+        <v>7103864</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3227,15 +3117,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>101709181</v>
+        <v>101709206</v>
       </c>
       <c r="B24" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3243,21 +3128,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3265,26 +3150,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>pulli/nyligen flygga ungar</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lillberget, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>716528.3681448691</v>
+        <v>716592</v>
       </c>
       <c r="R24" t="n">
-        <v>7103693.082254847</v>
+        <v>7103821</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3327,11 +3202,6 @@
       <c r="AB24" t="inlineStr">
         <is>
           <t>23:45</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>En unge</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3358,37 +3228,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>101709224</v>
+        <v>101709195</v>
       </c>
       <c r="B25" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3402,10 +3267,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>716450.908452035</v>
+        <v>716767</v>
       </c>
       <c r="R25" t="n">
-        <v>7103672.283088349</v>
+        <v>7103864</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3474,15 +3339,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>101709199</v>
+        <v>101709196</v>
       </c>
       <c r="B26" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3490,26 +3350,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3518,10 +3378,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>716562.9682073668</v>
+        <v>716593</v>
       </c>
       <c r="R26" t="n">
-        <v>7103797.627283255</v>
+        <v>7103820</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3590,15 +3450,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>101709196</v>
+        <v>101709181</v>
       </c>
       <c r="B27" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3606,21 +3461,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>102612</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3628,16 +3483,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lillberget, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>716592.7113790906</v>
+        <v>716529</v>
       </c>
       <c r="R27" t="n">
-        <v>7103819.948876309</v>
+        <v>7103693</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3680,6 +3545,11 @@
       <c r="AB27" t="inlineStr">
         <is>
           <t>23:45</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>En unge</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3706,42 +3576,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>101709232</v>
+        <v>101709238</v>
       </c>
       <c r="B28" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3750,10 +3615,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>716591.7799110597</v>
+        <v>716561</v>
       </c>
       <c r="R28" t="n">
-        <v>7103675.043594524</v>
+        <v>7103802</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3822,15 +3687,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>101709240</v>
+        <v>101709239</v>
       </c>
       <c r="B29" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3838,21 +3698,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2869</v>
+        <v>219790</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3866,10 +3726,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>716483.7784979482</v>
+        <v>716560</v>
       </c>
       <c r="R29" t="n">
-        <v>7103592.6822671</v>
+        <v>7103812</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3938,42 +3798,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>101709225</v>
+        <v>101709199</v>
       </c>
       <c r="B30" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3982,10 +3837,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>716466.0933646439</v>
+        <v>716563</v>
       </c>
       <c r="R30" t="n">
-        <v>7103650.446451461</v>
+        <v>7103798</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4054,42 +3909,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>101709206</v>
+        <v>101709200</v>
       </c>
       <c r="B31" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4098,10 +3948,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>716591.742511127</v>
+        <v>716561</v>
       </c>
       <c r="R31" t="n">
-        <v>7103821.202120564</v>
+        <v>7103802</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4167,122 +4017,6 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>101709223</v>
-      </c>
-      <c r="B32" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Lillberget, Vb</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>716418.3892741385</v>
-      </c>
-      <c r="R32" t="n">
-        <v>7103689.831937376</v>
-      </c>
-      <c r="S32" t="n">
-        <v>5</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>23:45</t>
-        </is>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24124-2024 artfynd.xlsx
+++ b/artfynd/A 24124-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101709190</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101709204</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101709240</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101709241</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101709242</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101709217</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1449,6 +1484,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101709219</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1560,6 +1600,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101709220</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1671,6 +1716,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101709222</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1782,6 +1832,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101709223</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1893,6 +1948,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101709224</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2004,6 +2064,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101709225</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2115,6 +2180,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101709227</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2226,6 +2296,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101709229</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2337,6 +2412,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101709230</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2448,6 +2528,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101709232</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2559,6 +2644,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101709233</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2670,6 +2760,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101709234</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2781,6 +2876,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101709235</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2892,6 +2992,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101709202</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3003,6 +3108,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101709203</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3114,6 +3224,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101709205</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3225,6 +3340,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101709206</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3336,6 +3456,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101709195</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3447,6 +3572,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101709196</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3573,6 +3703,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101709181</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3684,6 +3819,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101709238</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3795,6 +3935,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101709239</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3906,6 +4051,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101709199</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4017,8 +4167,45 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101709200</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>